--- a/pipeline_output/GOA_2W_H&M.xlsx
+++ b/pipeline_output/GOA_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8654,12 +8654,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9640,12 +9640,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10459,12 +10459,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
